--- a/data/forecast-births.xlsx
+++ b/data/forecast-births.xlsx
@@ -39,13 +39,13 @@
     <t>年份</t>
   </si>
   <si>
-    <t>低预测</t>
+    <t>低预测(万人)</t>
   </si>
   <si>
-    <t>中预测</t>
+    <t>中预测(万人)</t>
   </si>
   <si>
-    <t>高预测</t>
+    <t>高预测(万人)</t>
   </si>
 </sst>
 </file>
